--- a/docs/demo/AureonCare_Video_Library_Tracker.xlsx
+++ b/docs/demo/AureonCare_Video_Library_Tracker.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="298">
   <si>
     <t xml:space="preserve">AureonCare video library — production tracker</t>
   </si>
@@ -331,6 +331,9 @@
     <t xml:space="preserve">One-time cost that makes all 32 videos re-cuttable when the UI changes.</t>
   </si>
   <si>
+    <t xml:space="preserve">Harness at docs/demo/video-harness; re-run to re-cut</t>
+  </si>
+  <si>
     <t xml:space="preserve">V01</t>
   </si>
   <si>
@@ -347,6 +350,9 @@
   </si>
   <si>
     <t xml:space="preserve">The navigation model, so every later video can say 'go to X ▸ Y'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recorded; files in docs/demo/video-library/wave1. Awaiting SME review, then upload.</t>
   </si>
   <si>
     <t xml:space="preserve">V02</t>
@@ -1086,8 +1092,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1107,7 +1117,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1127,7 +1137,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1143,11 +1153,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1516,94 +1526,94 @@
   <dimension ref="B2:C18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="96"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1629,476 +1639,476 @@
   <dimension ref="B2:G42"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <f aca="false">COUNTA('Video Tracker'!$A$3:$A$41)</f>
         <v>39</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$B$3:$B$41,"&lt;&gt;Prep")</f>
         <v>38</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,"Published")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <f aca="false">COUNTA('Video Tracker'!$A$3:$A$41)-COUNTIF('Video Tracker'!$K$3:$K$41,"Not started")-COUNTIF('Video Tracker'!$K$3:$K$41,"Published")-COUNTIF('Video Tracker'!$K$3:$K$41,"On hold")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,"Not started")</f>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <f aca="false">IFERROR(AVERAGE('Video Tracker'!$P$3:$P$41),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
+        <v>0.173076923076923</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <f aca="false">SUM('Video Tracker'!$G$3:$G$41)</f>
         <v>68</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="9" t="n">
         <f aca="false">SUMIF('Video Tracker'!$K$3:$K$41,"Published",'Video Tracker'!$G$3:$G$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="9" t="s">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="10" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$B$3:$B$41,$B16)</f>
         <v>1</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <f aca="false">COUNTIFS('Video Tracker'!$B$3:$B$41,$B16,'Video Tracker'!$K$3:$K$41,"Published")</f>
         <v>0</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="13" t="n">
         <f aca="false">IFERROR(AVERAGEIF('Video Tracker'!$B$3:$B$41,$B16,'Video Tracker'!$P$3:$P$41),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F16" s="14" t="n">
         <f aca="false">SUMIF('Video Tracker'!$B$3:$B$41,$B16,'Video Tracker'!$G$3:$G$41)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$B$3:$B$41,$B17)</f>
         <v>8</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <f aca="false">COUNTIFS('Video Tracker'!$B$3:$B$41,$B17,'Video Tracker'!$K$3:$K$41,"Published")</f>
         <v>0</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="13" t="n">
         <f aca="false">IFERROR(AVERAGEIF('Video Tracker'!$B$3:$B$41,$B17,'Video Tracker'!$P$3:$P$41),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F17" s="14" t="n">
         <f aca="false">SUMIF('Video Tracker'!$B$3:$B$41,$B17,'Video Tracker'!$G$3:$G$41)</f>
         <v>13.5</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$B$3:$B$41,$B18)</f>
         <v>8</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="12" t="n">
         <f aca="false">COUNTIFS('Video Tracker'!$B$3:$B$41,$B18,'Video Tracker'!$K$3:$K$41,"Published")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="13" t="n">
         <f aca="false">IFERROR(AVERAGEIF('Video Tracker'!$B$3:$B$41,$B18,'Video Tracker'!$P$3:$P$41),0)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="14" t="n">
         <f aca="false">SUMIF('Video Tracker'!$B$3:$B$41,$B18,'Video Tracker'!$G$3:$G$41)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$B$3:$B$41,$B19)</f>
         <v>7</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="12" t="n">
         <f aca="false">COUNTIFS('Video Tracker'!$B$3:$B$41,$B19,'Video Tracker'!$K$3:$K$41,"Published")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="13" t="n">
         <f aca="false">IFERROR(AVERAGEIF('Video Tracker'!$B$3:$B$41,$B19,'Video Tracker'!$P$3:$P$41),0)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="14" t="n">
         <f aca="false">SUMIF('Video Tracker'!$B$3:$B$41,$B19,'Video Tracker'!$G$3:$G$41)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$B$3:$B$41,$B20)</f>
         <v>9</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="12" t="n">
         <f aca="false">COUNTIFS('Video Tracker'!$B$3:$B$41,$B20,'Video Tracker'!$K$3:$K$41,"Published")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="13" t="n">
         <f aca="false">IFERROR(AVERAGEIF('Video Tracker'!$B$3:$B$41,$B20,'Video Tracker'!$P$3:$P$41),0)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="F20" s="14" t="n">
         <f aca="false">SUMIF('Video Tracker'!$B$3:$B$41,$B20,'Video Tracker'!$G$3:$G$41)</f>
         <v>17</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$B$3:$B$41,$B21)</f>
         <v>6</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="12" t="n">
         <f aca="false">COUNTIFS('Video Tracker'!$B$3:$B$41,$B21,'Video Tracker'!$K$3:$K$41,"Published")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="13" t="n">
         <f aca="false">IFERROR(AVERAGEIF('Video Tracker'!$B$3:$B$41,$B21,'Video Tracker'!$P$3:$P$41),0)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="14" t="n">
         <f aca="false">SUMIF('Video Tracker'!$B$3:$B$41,$B21,'Video Tracker'!$G$3:$G$41)</f>
         <v>9.5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="9" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="10" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C25" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,$B25)</f>
-        <v>39</v>
-      </c>
-      <c r="D25" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D25" s="13" t="n">
         <f aca="false">IFERROR(C25/COUNTA('Video Tracker'!$A$3:$A$41),0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="10" t="s">
+        <v>0.769230769230769</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C26" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,$B26)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="13" t="n">
         <f aca="false">IFERROR(C26/COUNTA('Video Tracker'!$A$3:$A$41),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="C27" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,$B27)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="D27" s="13" t="n">
         <f aca="false">IFERROR(C27/COUNTA('Video Tracker'!$A$3:$A$41),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C28" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,$B28)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" s="13" t="n">
         <f aca="false">IFERROR(C28/COUNTA('Video Tracker'!$A$3:$A$41),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="C29" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,$B29)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" s="13" t="n">
         <f aca="false">IFERROR(C29/COUNTA('Video Tracker'!$A$3:$A$41),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="10" t="s">
+        <v>0.230769230769231</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,$B30)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D30" s="13" t="n">
         <f aca="false">IFERROR(C30/COUNTA('Video Tracker'!$A$3:$A$41),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="10" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C31" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,$B31)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="D31" s="13" t="n">
         <f aca="false">IFERROR(C31/COUNTA('Video Tracker'!$A$3:$A$41),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="10" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C32" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,$B32)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="D32" s="13" t="n">
         <f aca="false">IFERROR(C32/COUNTA('Video Tracker'!$A$3:$A$41),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="9" t="s">
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="10" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="11" t="n">
+      <c r="C36" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$L$3:$L$41,"Yes")</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D36" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$L$3:$L$41,"In progress")</f>
         <v>0</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$L$3:$L$41,"No")</f>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="11" t="n">
+      <c r="C37" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$M$3:$M$41,"Yes")</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D37" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$M$3:$M$41,"In progress")</f>
         <v>0</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$M$3:$M$41,"No")</f>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="11" t="n">
+      <c r="C38" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$N$3:$N$41,"Yes")</f>
-        <v>0</v>
-      </c>
-      <c r="D38" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$N$3:$N$41,"In progress")</f>
         <v>0</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$N$3:$N$41,"No")</f>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="11" t="n">
+      <c r="C39" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$O$3:$O$41,"Yes")</f>
         <v>0</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$O$3:$O$41,"In progress")</f>
         <v>0</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$O$3:$O$41,"No")</f>
         <v>39</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="14" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="15" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2128,126 +2138,126 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="15" t="s">
+      <c r="B2" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="16" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2270,2447 +2280,2483 @@
   <dimension ref="A1:V41"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="R2" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="S2" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="T2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="U2" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="V2" s="9" t="s">
+      <c r="V2" s="10" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="17" t="s">
+      <c r="G3" s="19"/>
+      <c r="H3" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="J3" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="K3" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M3" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N3" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O3" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P3" s="21" t="n">
+      <c r="J3" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P3" s="22" t="n">
         <f aca="false">COUNTIF(L3:O3,"Yes")/4</f>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="23" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="Q3" s="23" t="n">
+        <v>46235</v>
+      </c>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="24" t="str">
         <f aca="true">IF(S3&lt;&gt;"","",IF(R3="","",R3-TODAY()))</f>
         <v/>
       </c>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="A4" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="17" t="s">
+      <c r="D4" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="E4" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="F4" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H4" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="I4" s="17" t="s">
+      <c r="H4" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M4" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N4" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O4" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P4" s="21" t="n">
+      <c r="I4" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" s="22" t="n">
         <f aca="false">COUNTIF(L4:O4,"Yes")/4</f>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="23" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="Q4" s="23" t="n">
+        <v>46235</v>
+      </c>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="24" t="str">
         <f aca="true">IF(S4&lt;&gt;"","",IF(R4="","",R4-TODAY()))</f>
         <v/>
       </c>
-      <c r="U4" s="24"/>
-      <c r="V4" s="24"/>
+      <c r="U4" s="25"/>
+      <c r="V4" s="25" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="16" t="s">
+      <c r="A5" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="17" t="s">
+      <c r="D5" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="E5" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="G5" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H5" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="K5" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M5" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N5" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O5" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P5" s="21" t="n">
+      <c r="H5" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="O5" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P5" s="22" t="n">
         <f aca="false">COUNTIF(L5:O5,"Yes")/4</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="23" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="Q5" s="23" t="n">
+        <v>46235</v>
+      </c>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="24" t="str">
         <f aca="true">IF(S5&lt;&gt;"","",IF(R5="","",R5-TODAY()))</f>
         <v/>
       </c>
-      <c r="U5" s="24"/>
-      <c r="V5" s="24"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B6" s="16" t="s">
+      <c r="A6" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="18" t="n">
+      <c r="D6" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="K6" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M6" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N6" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O6" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P6" s="21" t="n">
+      <c r="H6" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N6" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P6" s="22" t="n">
         <f aca="false">COUNTIF(L6:O6,"Yes")/4</f>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="23" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="Q6" s="23" t="n">
+        <v>46235</v>
+      </c>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="24" t="str">
         <f aca="true">IF(S6&lt;&gt;"","",IF(R6="","",R6-TODAY()))</f>
         <v/>
       </c>
-      <c r="U6" s="24"/>
-      <c r="V6" s="24"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="16" t="s">
+      <c r="A7" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G7" s="18" t="n">
+      <c r="D7" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="K7" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P7" s="21" t="n">
+      <c r="H7" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N7" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="O7" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P7" s="22" t="n">
         <f aca="false">COUNTIF(L7:O7,"Yes")/4</f>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="23" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="Q7" s="23" t="n">
+        <v>46235</v>
+      </c>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="24" t="str">
         <f aca="true">IF(S7&lt;&gt;"","",IF(R7="","",R7-TODAY()))</f>
         <v/>
       </c>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="A8" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="G8" s="18" t="n">
+      <c r="D8" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N8" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O8" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P8" s="21" t="n">
+      <c r="H8" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N8" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="O8" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P8" s="22" t="n">
         <f aca="false">COUNTIF(L8:O8,"Yes")/4</f>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="23" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="Q8" s="23" t="n">
+        <v>46235</v>
+      </c>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
+      <c r="T8" s="24" t="str">
         <f aca="true">IF(S8&lt;&gt;"","",IF(R8="","",R8-TODAY()))</f>
         <v/>
       </c>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="B9" s="16" t="s">
+      <c r="A9" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="G9" s="18" t="n">
+      <c r="D9" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M9" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N9" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O9" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P9" s="21" t="n">
+      <c r="H9" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="O9" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P9" s="22" t="n">
         <f aca="false">COUNTIF(L9:O9,"Yes")/4</f>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="23" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="Q9" s="23" t="n">
+        <v>46235</v>
+      </c>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="24" t="str">
         <f aca="true">IF(S9&lt;&gt;"","",IF(R9="","",R9-TODAY()))</f>
         <v/>
       </c>
-      <c r="U9" s="24"/>
-      <c r="V9" s="24"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="A10" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="F10" s="17" t="s">
+      <c r="D10" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="E10" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G10" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="K10" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N10" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O10" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P10" s="21" t="n">
+      <c r="H10" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N10" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="O10" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" s="22" t="n">
         <f aca="false">COUNTIF(L10:O10,"Yes")/4</f>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="23" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="Q10" s="23" t="n">
+        <v>46235</v>
+      </c>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="24" t="str">
         <f aca="true">IF(S10&lt;&gt;"","",IF(R10="","",R10-TODAY()))</f>
         <v/>
       </c>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B11" s="16" t="s">
+      <c r="A11" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="B11" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="F11" s="17" t="s">
+      <c r="D11" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="E11" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H11" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="K11" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N11" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O11" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P11" s="21" t="n">
+      <c r="H11" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N11" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="O11" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P11" s="22" t="n">
         <f aca="false">COUNTIF(L11:O11,"Yes")/4</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="23" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="Q11" s="23" t="n">
+        <v>46235</v>
+      </c>
+      <c r="R11" s="23"/>
+      <c r="S11" s="23"/>
+      <c r="T11" s="24" t="str">
         <f aca="true">IF(S11&lt;&gt;"","",IF(R11="","",R11-TODAY()))</f>
         <v/>
       </c>
-      <c r="U11" s="24"/>
-      <c r="V11" s="24"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="B12" s="16" t="s">
+      <c r="A12" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="G12" s="18" t="n">
+      <c r="D12" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="J12" s="19" t="s">
+      <c r="H12" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="J12" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K12" s="20" t="s">
+      <c r="K12" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L12" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N12" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O12" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P12" s="21" t="n">
+      <c r="L12" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N12" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P12" s="22" t="n">
         <f aca="false">COUNTIF(L12:O12,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="23" t="str">
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
+      <c r="T12" s="24" t="str">
         <f aca="true">IF(S12&lt;&gt;"","",IF(R12="","",R12-TODAY()))</f>
         <v/>
       </c>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="B13" s="16" t="s">
+      <c r="A13" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="G13" s="18" t="n">
+      <c r="D13" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="J13" s="19" t="s">
+      <c r="H13" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="J13" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K13" s="20" t="s">
+      <c r="K13" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L13" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M13" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N13" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O13" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P13" s="21" t="n">
+      <c r="L13" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O13" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P13" s="22" t="n">
         <f aca="false">COUNTIF(L13:O13,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="23" t="str">
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="24" t="str">
         <f aca="true">IF(S13&lt;&gt;"","",IF(R13="","",R13-TODAY()))</f>
         <v/>
       </c>
-      <c r="U13" s="24"/>
-      <c r="V13" s="24"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="A14" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="G14" s="18" t="n">
+      <c r="D14" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G14" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H14" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="J14" s="19" t="s">
+      <c r="H14" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="J14" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K14" s="20" t="s">
+      <c r="K14" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L14" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M14" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N14" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O14" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P14" s="21" t="n">
+      <c r="L14" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M14" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N14" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O14" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P14" s="22" t="n">
         <f aca="false">COUNTIF(L14:O14,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="23" t="str">
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="24" t="str">
         <f aca="true">IF(S14&lt;&gt;"","",IF(R14="","",R14-TODAY()))</f>
         <v/>
       </c>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="B15" s="16" t="s">
+      <c r="A15" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="F15" s="17" t="s">
+      <c r="D15" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="E15" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="G15" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="J15" s="19" t="s">
+      <c r="H15" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="J15" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M15" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N15" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O15" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P15" s="21" t="n">
+      <c r="L15" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N15" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O15" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P15" s="22" t="n">
         <f aca="false">COUNTIF(L15:O15,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="23" t="str">
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="24" t="str">
         <f aca="true">IF(S15&lt;&gt;"","",IF(R15="","",R15-TODAY()))</f>
         <v/>
       </c>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
     </row>
     <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B16" s="16" t="s">
+      <c r="A16" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="G16" s="18" t="n">
+      <c r="D16" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="J16" s="19" t="s">
+      <c r="H16" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="J16" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K16" s="20" t="s">
+      <c r="K16" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L16" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M16" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N16" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O16" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P16" s="21" t="n">
+      <c r="L16" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N16" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O16" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P16" s="22" t="n">
         <f aca="false">COUNTIF(L16:O16,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
-      <c r="T16" s="23" t="str">
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="24" t="str">
         <f aca="true">IF(S16&lt;&gt;"","",IF(R16="","",R16-TODAY()))</f>
         <v/>
       </c>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B17" s="16" t="s">
+      <c r="A17" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="B17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="G17" s="18" t="n">
+      <c r="D17" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="J17" s="19" t="s">
+      <c r="H17" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="J17" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K17" s="20" t="s">
+      <c r="K17" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L17" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M17" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N17" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O17" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P17" s="21" t="n">
+      <c r="L17" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M17" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N17" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O17" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P17" s="22" t="n">
         <f aca="false">COUNTIF(L17:O17,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="23" t="str">
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="24" t="str">
         <f aca="true">IF(S17&lt;&gt;"","",IF(R17="","",R17-TODAY()))</f>
         <v/>
       </c>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="B18" s="16" t="s">
+      <c r="A18" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="G18" s="18" t="n">
+      <c r="D18" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H18" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="J18" s="19" t="s">
+      <c r="H18" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="J18" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K18" s="20" t="s">
+      <c r="K18" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L18" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M18" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N18" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O18" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P18" s="21" t="n">
+      <c r="L18" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N18" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O18" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P18" s="22" t="n">
         <f aca="false">COUNTIF(L18:O18,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="22"/>
-      <c r="T18" s="23" t="str">
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="24" t="str">
         <f aca="true">IF(S18&lt;&gt;"","",IF(R18="","",R18-TODAY()))</f>
         <v/>
       </c>
-      <c r="U18" s="24"/>
-      <c r="V18" s="24"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="25"/>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="B19" s="16" t="s">
+      <c r="A19" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="F19" s="17" t="s">
+      <c r="D19" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="E19" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="G19" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="J19" s="19" t="s">
+      <c r="H19" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="J19" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K19" s="20" t="s">
+      <c r="K19" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L19" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M19" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N19" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O19" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P19" s="21" t="n">
+      <c r="L19" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N19" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O19" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P19" s="22" t="n">
         <f aca="false">COUNTIF(L19:O19,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="22"/>
-      <c r="R19" s="22"/>
-      <c r="S19" s="22"/>
-      <c r="T19" s="23" t="str">
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
+      <c r="S19" s="23"/>
+      <c r="T19" s="24" t="str">
         <f aca="true">IF(S19&lt;&gt;"","",IF(R19="","",R19-TODAY()))</f>
         <v/>
       </c>
-      <c r="U19" s="24"/>
-      <c r="V19" s="24"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B20" s="16" t="s">
+      <c r="A20" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="F20" s="17" t="s">
+      <c r="D20" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="E20" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="G20" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="J20" s="19" t="s">
+      <c r="H20" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="J20" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L20" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M20" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N20" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O20" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P20" s="21" t="n">
+      <c r="L20" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N20" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O20" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P20" s="22" t="n">
         <f aca="false">COUNTIF(L20:O20,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="22"/>
-      <c r="R20" s="22"/>
-      <c r="S20" s="22"/>
-      <c r="T20" s="23" t="str">
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
+      <c r="S20" s="23"/>
+      <c r="T20" s="24" t="str">
         <f aca="true">IF(S20&lt;&gt;"","",IF(R20="","",R20-TODAY()))</f>
         <v/>
       </c>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
+      <c r="U20" s="25"/>
+      <c r="V20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="B21" s="16" t="s">
+      <c r="A21" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="G21" s="18" t="n">
+      <c r="D21" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="G21" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H21" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="J21" s="19" t="s">
+      <c r="H21" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="J21" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K21" s="20" t="s">
+      <c r="K21" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L21" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M21" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N21" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O21" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P21" s="21" t="n">
+      <c r="L21" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M21" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N21" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O21" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P21" s="22" t="n">
         <f aca="false">COUNTIF(L21:O21,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="22"/>
-      <c r="R21" s="22"/>
-      <c r="S21" s="22"/>
-      <c r="T21" s="23" t="str">
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
+      <c r="S21" s="23"/>
+      <c r="T21" s="24" t="str">
         <f aca="true">IF(S21&lt;&gt;"","",IF(R21="","",R21-TODAY()))</f>
         <v/>
       </c>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="B22" s="16" t="s">
+      <c r="A22" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="18" t="n">
+      <c r="D22" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="J22" s="19" t="s">
+      <c r="H22" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="J22" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K22" s="20" t="s">
+      <c r="K22" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L22" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M22" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N22" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O22" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P22" s="21" t="n">
+      <c r="L22" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N22" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O22" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P22" s="22" t="n">
         <f aca="false">COUNTIF(L22:O22,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="22"/>
-      <c r="R22" s="22"/>
-      <c r="S22" s="22"/>
-      <c r="T22" s="23" t="str">
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="24" t="str">
         <f aca="true">IF(S22&lt;&gt;"","",IF(R22="","",R22-TODAY()))</f>
         <v/>
       </c>
-      <c r="U22" s="24"/>
-      <c r="V22" s="24"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="25"/>
     </row>
     <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="B23" s="16" t="s">
+      <c r="A23" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B23" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="G23" s="18" t="n">
+      <c r="D23" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="G23" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="J23" s="19" t="s">
+      <c r="H23" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="J23" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K23" s="20" t="s">
+      <c r="K23" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L23" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M23" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N23" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O23" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P23" s="21" t="n">
+      <c r="L23" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N23" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O23" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P23" s="22" t="n">
         <f aca="false">COUNTIF(L23:O23,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
-      <c r="T23" s="23" t="str">
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="24" t="str">
         <f aca="true">IF(S23&lt;&gt;"","",IF(R23="","",R23-TODAY()))</f>
         <v/>
       </c>
-      <c r="U23" s="24"/>
-      <c r="V23" s="24"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
     </row>
     <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="B24" s="16" t="s">
+      <c r="A24" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="F24" s="17" t="s">
+      <c r="D24" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="G24" s="18" t="n">
+      <c r="E24" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="G24" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H24" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="J24" s="19" t="s">
+      <c r="H24" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="I24" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="J24" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K24" s="20" t="s">
+      <c r="K24" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L24" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M24" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N24" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O24" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P24" s="21" t="n">
+      <c r="L24" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N24" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O24" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P24" s="22" t="n">
         <f aca="false">COUNTIF(L24:O24,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="22"/>
-      <c r="R24" s="22"/>
-      <c r="S24" s="22"/>
-      <c r="T24" s="23" t="str">
+      <c r="Q24" s="23"/>
+      <c r="R24" s="23"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="24" t="str">
         <f aca="true">IF(S24&lt;&gt;"","",IF(R24="","",R24-TODAY()))</f>
         <v/>
       </c>
-      <c r="U24" s="24"/>
-      <c r="V24" s="24"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
     </row>
     <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="B25" s="16" t="s">
+      <c r="A25" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="B25" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="G25" s="18" t="n">
+      <c r="D25" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="G25" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="I25" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="J25" s="19" t="s">
+      <c r="H25" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="J25" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K25" s="20" t="s">
+      <c r="K25" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L25" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M25" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N25" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O25" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P25" s="21" t="n">
+      <c r="L25" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M25" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N25" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O25" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P25" s="22" t="n">
         <f aca="false">COUNTIF(L25:O25,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="22"/>
-      <c r="S25" s="22"/>
-      <c r="T25" s="23" t="str">
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
+      <c r="S25" s="23"/>
+      <c r="T25" s="24" t="str">
         <f aca="true">IF(S25&lt;&gt;"","",IF(R25="","",R25-TODAY()))</f>
         <v/>
       </c>
-      <c r="U25" s="24"/>
-      <c r="V25" s="24"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="25"/>
     </row>
     <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="B26" s="16" t="s">
+      <c r="A26" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="G26" s="18" t="n">
+      <c r="D26" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="G26" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="J26" s="19" t="s">
+      <c r="H26" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="I26" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="J26" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K26" s="20" t="s">
+      <c r="K26" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L26" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N26" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O26" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P26" s="21" t="n">
+      <c r="L26" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N26" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O26" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P26" s="22" t="n">
         <f aca="false">COUNTIF(L26:O26,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q26" s="22"/>
-      <c r="R26" s="22"/>
-      <c r="S26" s="22"/>
-      <c r="T26" s="23" t="str">
+      <c r="Q26" s="23"/>
+      <c r="R26" s="23"/>
+      <c r="S26" s="23"/>
+      <c r="T26" s="24" t="str">
         <f aca="true">IF(S26&lt;&gt;"","",IF(R26="","",R26-TODAY()))</f>
         <v/>
       </c>
-      <c r="U26" s="24"/>
-      <c r="V26" s="24"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="25"/>
     </row>
     <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="B27" s="16" t="s">
+      <c r="A27" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="G27" s="18" t="n">
+      <c r="D27" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="G27" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="I27" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="J27" s="19" t="s">
+      <c r="H27" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="J27" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K27" s="20" t="s">
+      <c r="K27" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P27" s="21" t="n">
+      <c r="L27" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M27" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N27" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O27" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P27" s="22" t="n">
         <f aca="false">COUNTIF(L27:O27,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="22"/>
-      <c r="S27" s="22"/>
-      <c r="T27" s="23" t="str">
+      <c r="Q27" s="23"/>
+      <c r="R27" s="23"/>
+      <c r="S27" s="23"/>
+      <c r="T27" s="24" t="str">
         <f aca="true">IF(S27&lt;&gt;"","",IF(R27="","",R27-TODAY()))</f>
         <v/>
       </c>
-      <c r="U27" s="24"/>
-      <c r="V27" s="24"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="25"/>
     </row>
     <row r="28" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="B28" s="16" t="s">
+      <c r="A28" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="B28" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="G28" s="18" t="n">
+      <c r="D28" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="G28" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="I28" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="J28" s="19" t="s">
+      <c r="H28" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="J28" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K28" s="20" t="s">
+      <c r="K28" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L28" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M28" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N28" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O28" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P28" s="21" t="n">
+      <c r="L28" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M28" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N28" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O28" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P28" s="22" t="n">
         <f aca="false">COUNTIF(L28:O28,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="22"/>
-      <c r="S28" s="22"/>
-      <c r="T28" s="23" t="str">
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="24" t="str">
         <f aca="true">IF(S28&lt;&gt;"","",IF(R28="","",R28-TODAY()))</f>
         <v/>
       </c>
-      <c r="U28" s="24"/>
-      <c r="V28" s="24"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B29" s="16" t="s">
+      <c r="A29" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="B29" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="G29" s="18" t="n">
+      <c r="D29" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="G29" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H29" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="I29" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="J29" s="19" t="s">
+      <c r="H29" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="I29" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="J29" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K29" s="20" t="s">
+      <c r="K29" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L29" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M29" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N29" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O29" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P29" s="21" t="n">
+      <c r="L29" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M29" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N29" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O29" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P29" s="22" t="n">
         <f aca="false">COUNTIF(L29:O29,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="22"/>
-      <c r="R29" s="22"/>
-      <c r="S29" s="22"/>
-      <c r="T29" s="23" t="str">
+      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
+      <c r="S29" s="23"/>
+      <c r="T29" s="24" t="str">
         <f aca="true">IF(S29&lt;&gt;"","",IF(R29="","",R29-TODAY()))</f>
         <v/>
       </c>
-      <c r="U29" s="24"/>
-      <c r="V29" s="24"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="B30" s="16" t="s">
+      <c r="A30" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D30" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="G30" s="18" t="n">
+      <c r="D30" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="G30" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="I30" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="J30" s="19" t="s">
+      <c r="H30" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="J30" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K30" s="20" t="s">
+      <c r="K30" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L30" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M30" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N30" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O30" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P30" s="21" t="n">
+      <c r="L30" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M30" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O30" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P30" s="22" t="n">
         <f aca="false">COUNTIF(L30:O30,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="22"/>
-      <c r="R30" s="22"/>
-      <c r="S30" s="22"/>
-      <c r="T30" s="23" t="str">
+      <c r="Q30" s="23"/>
+      <c r="R30" s="23"/>
+      <c r="S30" s="23"/>
+      <c r="T30" s="24" t="str">
         <f aca="true">IF(S30&lt;&gt;"","",IF(R30="","",R30-TODAY()))</f>
         <v/>
       </c>
-      <c r="U30" s="24"/>
-      <c r="V30" s="24"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="25"/>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="B31" s="16" t="s">
+      <c r="A31" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="B31" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="F31" s="17" t="s">
+      <c r="D31" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="G31" s="18" t="n">
+      <c r="E31" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="G31" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="17" t="s">
-        <v>248</v>
-      </c>
-      <c r="I31" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="J31" s="19" t="s">
+      <c r="H31" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="I31" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="J31" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K31" s="20" t="s">
+      <c r="K31" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L31" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M31" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N31" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O31" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P31" s="21" t="n">
+      <c r="L31" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N31" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O31" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P31" s="22" t="n">
         <f aca="false">COUNTIF(L31:O31,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="22"/>
-      <c r="R31" s="22"/>
-      <c r="S31" s="22"/>
-      <c r="T31" s="23" t="str">
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="24" t="str">
         <f aca="true">IF(S31&lt;&gt;"","",IF(R31="","",R31-TODAY()))</f>
         <v/>
       </c>
-      <c r="U31" s="24"/>
-      <c r="V31" s="24"/>
+      <c r="U31" s="25"/>
+      <c r="V31" s="25"/>
     </row>
     <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="B32" s="16" t="s">
+      <c r="A32" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="B32" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="F32" s="17" t="s">
+      <c r="D32" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="G32" s="18" t="n">
+      <c r="E32" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="G32" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H32" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="I32" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="J32" s="19" t="s">
+      <c r="H32" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="J32" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K32" s="20" t="s">
+      <c r="K32" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L32" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M32" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N32" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O32" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P32" s="21" t="n">
+      <c r="L32" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N32" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O32" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P32" s="22" t="n">
         <f aca="false">COUNTIF(L32:O32,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q32" s="22"/>
-      <c r="R32" s="22"/>
-      <c r="S32" s="22"/>
-      <c r="T32" s="23" t="str">
+      <c r="Q32" s="23"/>
+      <c r="R32" s="23"/>
+      <c r="S32" s="23"/>
+      <c r="T32" s="24" t="str">
         <f aca="true">IF(S32&lt;&gt;"","",IF(R32="","",R32-TODAY()))</f>
         <v/>
       </c>
-      <c r="U32" s="24"/>
-      <c r="V32" s="24"/>
+      <c r="U32" s="25"/>
+      <c r="V32" s="25"/>
     </row>
     <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="B33" s="16" t="s">
+      <c r="A33" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D33" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="F33" s="17" t="s">
+      <c r="D33" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="G33" s="18" t="n">
+      <c r="E33" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="G33" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H33" s="17" t="s">
-        <v>260</v>
-      </c>
-      <c r="I33" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="J33" s="19" t="s">
+      <c r="H33" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="J33" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K33" s="20" t="s">
+      <c r="K33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L33" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M33" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N33" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O33" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P33" s="21" t="n">
+      <c r="L33" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M33" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N33" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O33" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P33" s="22" t="n">
         <f aca="false">COUNTIF(L33:O33,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q33" s="22"/>
-      <c r="R33" s="22"/>
-      <c r="S33" s="22"/>
-      <c r="T33" s="23" t="str">
+      <c r="Q33" s="23"/>
+      <c r="R33" s="23"/>
+      <c r="S33" s="23"/>
+      <c r="T33" s="24" t="str">
         <f aca="true">IF(S33&lt;&gt;"","",IF(R33="","",R33-TODAY()))</f>
         <v/>
       </c>
-      <c r="U33" s="24"/>
-      <c r="V33" s="24"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="25"/>
     </row>
     <row r="34" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="B34" s="16" t="s">
+      <c r="A34" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="B34" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="F34" s="17" t="s">
+      <c r="D34" s="18" t="s">
         <v>265</v>
       </c>
-      <c r="G34" s="18" t="n">
+      <c r="E34" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="G34" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="I34" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="J34" s="19" t="s">
+      <c r="H34" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="J34" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K34" s="20" t="s">
+      <c r="K34" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L34" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M34" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N34" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O34" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P34" s="21" t="n">
+      <c r="L34" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M34" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N34" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O34" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P34" s="22" t="n">
         <f aca="false">COUNTIF(L34:O34,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="22"/>
-      <c r="R34" s="22"/>
-      <c r="S34" s="22"/>
-      <c r="T34" s="23" t="str">
+      <c r="Q34" s="23"/>
+      <c r="R34" s="23"/>
+      <c r="S34" s="23"/>
+      <c r="T34" s="24" t="str">
         <f aca="true">IF(S34&lt;&gt;"","",IF(R34="","",R34-TODAY()))</f>
         <v/>
       </c>
-      <c r="U34" s="24"/>
-      <c r="V34" s="24"/>
+      <c r="U34" s="25"/>
+      <c r="V34" s="25"/>
     </row>
     <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="B35" s="16" t="s">
+      <c r="A35" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="B35" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D35" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="F35" s="17" t="s">
+      <c r="D35" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="G35" s="18" t="n">
+      <c r="E35" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="G35" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="I35" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="J35" s="19" t="s">
+      <c r="H35" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="I35" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="J35" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K35" s="20" t="s">
+      <c r="K35" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L35" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M35" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N35" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O35" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P35" s="21" t="n">
+      <c r="L35" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M35" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N35" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O35" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P35" s="22" t="n">
         <f aca="false">COUNTIF(L35:O35,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="22"/>
-      <c r="S35" s="22"/>
-      <c r="T35" s="23" t="str">
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
+      <c r="S35" s="23"/>
+      <c r="T35" s="24" t="str">
         <f aca="true">IF(S35&lt;&gt;"","",IF(R35="","",R35-TODAY()))</f>
         <v/>
       </c>
-      <c r="U35" s="24"/>
-      <c r="V35" s="24"/>
+      <c r="U35" s="25"/>
+      <c r="V35" s="25"/>
     </row>
     <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="B36" s="16" t="s">
+      <c r="A36" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="B36" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="F36" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G36" s="18" t="n">
+      <c r="D36" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G36" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H36" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="I36" s="17"/>
-      <c r="J36" s="19" t="s">
+      <c r="H36" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="I36" s="18"/>
+      <c r="J36" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K36" s="20" t="s">
+      <c r="K36" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L36" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M36" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N36" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O36" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P36" s="21" t="n">
+      <c r="L36" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M36" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N36" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O36" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P36" s="22" t="n">
         <f aca="false">COUNTIF(L36:O36,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q36" s="22"/>
-      <c r="R36" s="22"/>
-      <c r="S36" s="22"/>
-      <c r="T36" s="23" t="str">
+      <c r="Q36" s="23"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="23"/>
+      <c r="T36" s="24" t="str">
         <f aca="true">IF(S36&lt;&gt;"","",IF(R36="","",R36-TODAY()))</f>
         <v/>
       </c>
-      <c r="U36" s="24"/>
-      <c r="V36" s="24"/>
+      <c r="U36" s="25"/>
+      <c r="V36" s="25"/>
     </row>
     <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="B37" s="16" t="s">
+      <c r="A37" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="B37" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="G37" s="18" t="n">
+      <c r="D37" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="G37" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H37" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="I37" s="17"/>
-      <c r="J37" s="19" t="s">
+      <c r="H37" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="I37" s="18"/>
+      <c r="J37" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K37" s="20" t="s">
+      <c r="K37" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L37" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M37" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N37" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O37" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P37" s="21" t="n">
+      <c r="L37" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M37" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N37" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O37" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P37" s="22" t="n">
         <f aca="false">COUNTIF(L37:O37,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q37" s="22"/>
-      <c r="R37" s="22"/>
-      <c r="S37" s="22"/>
-      <c r="T37" s="23" t="str">
+      <c r="Q37" s="23"/>
+      <c r="R37" s="23"/>
+      <c r="S37" s="23"/>
+      <c r="T37" s="24" t="str">
         <f aca="true">IF(S37&lt;&gt;"","",IF(R37="","",R37-TODAY()))</f>
         <v/>
       </c>
-      <c r="U37" s="24"/>
-      <c r="V37" s="24"/>
+      <c r="U37" s="25"/>
+      <c r="V37" s="25"/>
     </row>
     <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16" t="s">
-        <v>281</v>
-      </c>
-      <c r="B38" s="16" t="s">
+      <c r="A38" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="B38" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D38" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>283</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="G38" s="18" t="n">
+      <c r="D38" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G38" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H38" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="I38" s="17"/>
-      <c r="J38" s="19" t="s">
+      <c r="H38" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="I38" s="18"/>
+      <c r="J38" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K38" s="20" t="s">
+      <c r="K38" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L38" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M38" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N38" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O38" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P38" s="21" t="n">
+      <c r="L38" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M38" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N38" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O38" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P38" s="22" t="n">
         <f aca="false">COUNTIF(L38:O38,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q38" s="22"/>
-      <c r="R38" s="22"/>
-      <c r="S38" s="22"/>
-      <c r="T38" s="23" t="str">
+      <c r="Q38" s="23"/>
+      <c r="R38" s="23"/>
+      <c r="S38" s="23"/>
+      <c r="T38" s="24" t="str">
         <f aca="true">IF(S38&lt;&gt;"","",IF(R38="","",R38-TODAY()))</f>
         <v/>
       </c>
-      <c r="U38" s="24"/>
-      <c r="V38" s="24"/>
+      <c r="U38" s="25"/>
+      <c r="V38" s="25"/>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="B39" s="16" t="s">
+      <c r="A39" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="B39" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D39" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="G39" s="18" t="n">
+      <c r="D39" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="G39" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H39" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="I39" s="17"/>
-      <c r="J39" s="19" t="s">
+      <c r="H39" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="I39" s="18"/>
+      <c r="J39" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K39" s="20" t="s">
+      <c r="K39" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L39" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M39" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N39" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O39" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P39" s="21" t="n">
+      <c r="L39" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N39" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O39" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P39" s="22" t="n">
         <f aca="false">COUNTIF(L39:O39,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q39" s="22"/>
-      <c r="R39" s="22"/>
-      <c r="S39" s="22"/>
-      <c r="T39" s="23" t="str">
+      <c r="Q39" s="23"/>
+      <c r="R39" s="23"/>
+      <c r="S39" s="23"/>
+      <c r="T39" s="24" t="str">
         <f aca="true">IF(S39&lt;&gt;"","",IF(R39="","",R39-TODAY()))</f>
         <v/>
       </c>
-      <c r="U39" s="24"/>
-      <c r="V39" s="24"/>
+      <c r="U39" s="25"/>
+      <c r="V39" s="25"/>
     </row>
     <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="B40" s="16" t="s">
+      <c r="A40" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="B40" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G40" s="18" t="n">
+      <c r="D40" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G40" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H40" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="I40" s="17"/>
-      <c r="J40" s="19" t="s">
+      <c r="H40" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="I40" s="18"/>
+      <c r="J40" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K40" s="20" t="s">
+      <c r="K40" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L40" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M40" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N40" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O40" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P40" s="21" t="n">
+      <c r="L40" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M40" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N40" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O40" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P40" s="22" t="n">
         <f aca="false">COUNTIF(L40:O40,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q40" s="22"/>
-      <c r="R40" s="22"/>
-      <c r="S40" s="22"/>
-      <c r="T40" s="23" t="str">
+      <c r="Q40" s="23"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="24" t="str">
         <f aca="true">IF(S40&lt;&gt;"","",IF(R40="","",R40-TODAY()))</f>
         <v/>
       </c>
-      <c r="U40" s="24"/>
-      <c r="V40" s="24"/>
+      <c r="U40" s="25"/>
+      <c r="V40" s="25"/>
     </row>
     <row r="41" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="16" t="s">
-        <v>293</v>
-      </c>
-      <c r="B41" s="16" t="s">
+      <c r="A41" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="B41" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="G41" s="18" t="n">
+      <c r="D41" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="G41" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="H41" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="I41" s="17"/>
-      <c r="J41" s="19" t="s">
+      <c r="H41" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="I41" s="18"/>
+      <c r="J41" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K41" s="20" t="s">
+      <c r="K41" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L41" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M41" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N41" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O41" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P41" s="21" t="n">
+      <c r="L41" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M41" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N41" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O41" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P41" s="22" t="n">
         <f aca="false">COUNTIF(L41:O41,"Yes")/4</f>
         <v>0</v>
       </c>
-      <c r="Q41" s="22"/>
-      <c r="R41" s="22"/>
-      <c r="S41" s="22"/>
-      <c r="T41" s="23" t="str">
+      <c r="Q41" s="23"/>
+      <c r="R41" s="23"/>
+      <c r="S41" s="23"/>
+      <c r="T41" s="24" t="str">
         <f aca="true">IF(S41&lt;&gt;"","",IF(R41="","",R41-TODAY()))</f>
         <v/>
       </c>
-      <c r="U41" s="24"/>
-      <c r="V41" s="24"/>
+      <c r="U41" s="25"/>
+      <c r="V41" s="25"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:V41"/>
@@ -4739,7 +4785,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{618F3EAF-92CD-4E58-B2C1-B48DC25648D6}</x14:id>
+          <x14:id>{0010C0EB-B73B-4E00-BB55-CB82FE62DD52}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4778,7 +4824,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{618F3EAF-92CD-4E58-B2C1-B48DC25648D6}">
+          <x14:cfRule type="dataBar" id="{0010C0EB-B73B-4E00-BB55-CB82FE62DD52}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/docs/demo/AureonCare_Video_Library_Tracker.xlsx
+++ b/docs/demo/AureonCare_Video_Library_Tracker.xlsx
@@ -331,7 +331,7 @@
     <t xml:space="preserve">One-time cost that makes all 32 videos re-cuttable when the UI changes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Harness at docs/demo/video-harness; re-run to re-cut</t>
+    <t xml:space="preserve">Harness at docs/demo/video-harness — branding kit and narration pipeline included.</t>
   </si>
   <si>
     <t xml:space="preserve">V01</t>
@@ -352,7 +352,7 @@
     <t xml:space="preserve">The navigation model, so every later video can say 'go to X ▸ Y'.</t>
   </si>
   <si>
-    <t xml:space="preserve">Recorded; files in docs/demo/video-library/wave1. Awaiting SME review, then upload.</t>
+    <t xml:space="preserve">Recorded, branded (logo bumper, caption-bar mark, outro) and narrated. Voice is placeholder TTS — re-render with VOICE_ENGINE=files before publishing.</t>
   </si>
   <si>
     <t xml:space="preserve">V02</t>
@@ -4785,7 +4785,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0010C0EB-B73B-4E00-BB55-CB82FE62DD52}</x14:id>
+          <x14:id>{A57DDBEC-8F8C-44B0-8A69-46E154A8BDED}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4824,7 +4824,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0010C0EB-B73B-4E00-BB55-CB82FE62DD52}">
+          <x14:cfRule type="dataBar" id="{A57DDBEC-8F8C-44B0-8A69-46E154A8BDED}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/docs/demo/AureonCare_Video_Library_Tracker.xlsx
+++ b/docs/demo/AureonCare_Video_Library_Tracker.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="299">
   <si>
     <t xml:space="preserve">AureonCare video library — production tracker</t>
   </si>
@@ -568,13 +568,16 @@
     <t xml:space="preserve">Record a diagnosis</t>
   </si>
   <si>
-    <t xml:space="preserve">Patients ▸ Diagnoses</t>
+    <t xml:space="preserve">Clinical ▸ Diagnoses</t>
   </si>
   <si>
     <t xml:space="preserve">New diagnosis → ICD-10 search → status (active/resolved/chronic) → onset → link to encounter → flows onto claims and the portal.</t>
   </si>
   <si>
     <t xml:space="preserve">Diagnosis quality drives claim acceptance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recorded ahead of the rest of Wave 2, against the relocated nav (Clinical, not Patients) and the new patient picker on the form. Files in docs/demo/video-library/wave2.</t>
   </si>
   <si>
     <t xml:space="preserve">V16</t>
@@ -1698,7 +1701,7 @@
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">COUNTA('Video Tracker'!$A$3:$A$41)-COUNTIF('Video Tracker'!$K$3:$K$41,"Not started")-COUNTIF('Video Tracker'!$K$3:$K$41,"Published")-COUNTIF('Video Tracker'!$K$3:$K$41,"On hold")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1707,7 +1710,7 @@
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,"Not started")</f>
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1716,7 +1719,7 @@
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">IFERROR(AVERAGE('Video Tracker'!$P$3:$P$41),0)</f>
-        <v>0.173076923076923</v>
+        <v>0.192307692307692</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1725,7 +1728,7 @@
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">SUM('Video Tracker'!$G$3:$G$41)</f>
-        <v>68</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1820,11 +1823,11 @@
       </c>
       <c r="E18" s="13" t="n">
         <f aca="false">IFERROR(AVERAGEIF('Video Tracker'!$B$3:$B$41,$B18,'Video Tracker'!$P$3:$P$41),0)</f>
-        <v>0</v>
+        <v>0.09375</v>
       </c>
       <c r="F18" s="14" t="n">
         <f aca="false">SUMIF('Video Tracker'!$B$3:$B$41,$B18,'Video Tracker'!$G$3:$G$41)</f>
-        <v>15</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1917,11 +1920,11 @@
       </c>
       <c r="C25" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,$B25)</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" s="13" t="n">
         <f aca="false">IFERROR(C25/COUNTA('Video Tracker'!$A$3:$A$41),0)</f>
-        <v>0.769230769230769</v>
+        <v>0.743589743589744</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1969,11 +1972,11 @@
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$K$3:$K$41,$B29)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" s="13" t="n">
         <f aca="false">IFERROR(C29/COUNTA('Video Tracker'!$A$3:$A$41),0)</f>
-        <v>0.230769230769231</v>
+        <v>0.256410256410256</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2045,7 +2048,7 @@
       </c>
       <c r="C36" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$L$3:$L$41,"Yes")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$L$3:$L$41,"In progress")</f>
@@ -2053,7 +2056,7 @@
       </c>
       <c r="E36" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$L$3:$L$41,"No")</f>
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2062,7 +2065,7 @@
       </c>
       <c r="C37" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$M$3:$M$41,"Yes")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$M$3:$M$41,"In progress")</f>
@@ -2070,7 +2073,7 @@
       </c>
       <c r="E37" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$M$3:$M$41,"No")</f>
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2079,7 +2082,7 @@
       </c>
       <c r="C38" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$N$3:$N$41,"Yes")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$N$3:$N$41,"In progress")</f>
@@ -2087,7 +2090,7 @@
       </c>
       <c r="E38" s="12" t="n">
         <f aca="false">COUNTIF('Video Tracker'!$N$3:$N$41,"No")</f>
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3350,7 +3353,7 @@
         <v>127</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>181</v>
@@ -3359,28 +3362,30 @@
         <v>182</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M18" s="21" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N18" s="21" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="O18" s="21" t="s">
         <v>65</v>
       </c>
       <c r="P18" s="22" t="n">
         <f aca="false">COUNTIF(L18:O18,"Yes")/4</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="23"/>
+        <v>0.75</v>
+      </c>
+      <c r="Q18" s="23" t="n">
+        <v>46246</v>
+      </c>
       <c r="R18" s="23"/>
       <c r="S18" s="23"/>
       <c r="T18" s="24" t="str">
@@ -3388,11 +3393,13 @@
         <v/>
       </c>
       <c r="U18" s="25"/>
-      <c r="V18" s="25"/>
+      <c r="V18" s="25" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>38</v>
@@ -3401,22 +3408,22 @@
         <v>68</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G19" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I19" s="18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J19" s="20" t="s">
         <v>67</v>
@@ -3452,7 +3459,7 @@
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>39</v>
@@ -3461,22 +3468,22 @@
         <v>71</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G20" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J20" s="20" t="s">
         <v>67</v>
@@ -3512,7 +3519,7 @@
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>39</v>
@@ -3521,10 +3528,10 @@
         <v>71</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>112</v>
@@ -3533,10 +3540,10 @@
         <v>1.5</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J21" s="20" t="s">
         <v>67</v>
@@ -3572,7 +3579,7 @@
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>39</v>
@@ -3581,10 +3588,10 @@
         <v>71</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>112</v>
@@ -3593,10 +3600,10 @@
         <v>2</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J22" s="20" t="s">
         <v>67</v>
@@ -3632,7 +3639,7 @@
     </row>
     <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>39</v>
@@ -3641,22 +3648,22 @@
         <v>71</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G23" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J23" s="20" t="s">
         <v>67</v>
@@ -3692,7 +3699,7 @@
     </row>
     <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>39</v>
@@ -3701,22 +3708,22 @@
         <v>71</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G24" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J24" s="20" t="s">
         <v>67</v>
@@ -3752,7 +3759,7 @@
     </row>
     <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>39</v>
@@ -3761,22 +3768,22 @@
         <v>71</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G25" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J25" s="20" t="s">
         <v>67</v>
@@ -3812,7 +3819,7 @@
     </row>
     <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>39</v>
@@ -3821,22 +3828,22 @@
         <v>71</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G26" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J26" s="20" t="s">
         <v>67</v>
@@ -3872,7 +3879,7 @@
     </row>
     <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B27" s="17" t="s">
         <v>40</v>
@@ -3881,22 +3888,22 @@
         <v>73</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G27" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J27" s="20" t="s">
         <v>67</v>
@@ -3932,7 +3939,7 @@
     </row>
     <row r="28" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B28" s="17" t="s">
         <v>40</v>
@@ -3941,22 +3948,22 @@
         <v>73</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G28" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J28" s="20" t="s">
         <v>67</v>
@@ -3992,7 +3999,7 @@
     </row>
     <row r="29" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B29" s="17" t="s">
         <v>40</v>
@@ -4001,22 +4008,22 @@
         <v>73</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G29" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J29" s="20" t="s">
         <v>67</v>
@@ -4052,7 +4059,7 @@
     </row>
     <row r="30" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B30" s="17" t="s">
         <v>40</v>
@@ -4061,22 +4068,22 @@
         <v>73</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G30" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J30" s="20" t="s">
         <v>67</v>
@@ -4112,7 +4119,7 @@
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>40</v>
@@ -4121,22 +4128,22 @@
         <v>73</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G31" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J31" s="20" t="s">
         <v>67</v>
@@ -4172,7 +4179,7 @@
     </row>
     <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B32" s="17" t="s">
         <v>40</v>
@@ -4181,22 +4188,22 @@
         <v>73</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G32" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J32" s="20" t="s">
         <v>67</v>
@@ -4232,7 +4239,7 @@
     </row>
     <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B33" s="17" t="s">
         <v>40</v>
@@ -4241,22 +4248,22 @@
         <v>73</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G33" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J33" s="20" t="s">
         <v>67</v>
@@ -4292,7 +4299,7 @@
     </row>
     <row r="34" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B34" s="17" t="s">
         <v>40</v>
@@ -4301,22 +4308,22 @@
         <v>73</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G34" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J34" s="20" t="s">
         <v>67</v>
@@ -4352,7 +4359,7 @@
     </row>
     <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B35" s="17" t="s">
         <v>40</v>
@@ -4361,22 +4368,22 @@
         <v>73</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G35" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I35" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J35" s="20" t="s">
         <v>67</v>
@@ -4412,7 +4419,7 @@
     </row>
     <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>41</v>
@@ -4421,10 +4428,10 @@
         <v>75</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>105</v>
@@ -4433,7 +4440,7 @@
         <v>1.5</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I36" s="18"/>
       <c r="J36" s="20" t="s">
@@ -4470,7 +4477,7 @@
     </row>
     <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>41</v>
@@ -4479,7 +4486,7 @@
         <v>75</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>111</v>
@@ -4491,7 +4498,7 @@
         <v>1.5</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I37" s="18"/>
       <c r="J37" s="20" t="s">
@@ -4528,7 +4535,7 @@
     </row>
     <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>41</v>
@@ -4537,10 +4544,10 @@
         <v>75</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>127</v>
@@ -4549,7 +4556,7 @@
         <v>1.5</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I38" s="18"/>
       <c r="J38" s="20" t="s">
@@ -4586,7 +4593,7 @@
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B39" s="17" t="s">
         <v>41</v>
@@ -4595,19 +4602,19 @@
         <v>75</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G39" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I39" s="18"/>
       <c r="J39" s="20" t="s">
@@ -4644,7 +4651,7 @@
     </row>
     <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>41</v>
@@ -4653,10 +4660,10 @@
         <v>75</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>105</v>
@@ -4665,7 +4672,7 @@
         <v>1.5</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I40" s="18"/>
       <c r="J40" s="20" t="s">
@@ -4702,7 +4709,7 @@
     </row>
     <row r="41" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B41" s="17" t="s">
         <v>41</v>
@@ -4711,7 +4718,7 @@
         <v>75</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E41" s="18" t="s">
         <v>117</v>
@@ -4723,7 +4730,7 @@
         <v>1.5</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I41" s="18"/>
       <c r="J41" s="20" t="s">
@@ -4785,7 +4792,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A57DDBEC-8F8C-44B0-8A69-46E154A8BDED}</x14:id>
+          <x14:id>{9F52965E-A210-4A8B-A064-45EC999E553A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4824,7 +4831,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A57DDBEC-8F8C-44B0-8A69-46E154A8BDED}">
+          <x14:cfRule type="dataBar" id="{9F52965E-A210-4A8B-A064-45EC999E553A}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/docs/demo/AureonCare_Video_Library_Tracker.xlsx
+++ b/docs/demo/AureonCare_Video_Library_Tracker.xlsx
@@ -577,7 +577,7 @@
     <t xml:space="preserve">Diagnosis quality drives claim acceptance.</t>
   </si>
   <si>
-    <t xml:space="preserve">Recorded ahead of the rest of Wave 2, against the relocated nav (Clinical, not Patients) and the new patient picker on the form. Files in docs/demo/video-library/wave2.</t>
+    <t xml:space="preserve">Re-recorded against the relocated nav (Clinical, not Patients) and the new patient picker on the standalone form. Narrated with google/en-US-Neural2-D to match the rest of the library.</t>
   </si>
   <si>
     <t xml:space="preserve">V16</t>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">SUM('Video Tracker'!$G$3:$G$41)</f>
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F18" s="14" t="n">
         <f aca="false">SUMIF('Video Tracker'!$B$3:$B$41,$B18,'Video Tracker'!$G$3:$G$41)</f>
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3353,7 +3353,7 @@
         <v>127</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>181</v>
@@ -4792,7 +4792,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9F52965E-A210-4A8B-A064-45EC999E553A}</x14:id>
+          <x14:id>{389B8875-14B1-4113-ABEC-61DA4FC43B80}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4831,7 +4831,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9F52965E-A210-4A8B-A064-45EC999E553A}">
+          <x14:cfRule type="dataBar" id="{389B8875-14B1-4113-ABEC-61DA4FC43B80}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/docs/demo/AureonCare_Video_Library_Tracker.xlsx
+++ b/docs/demo/AureonCare_Video_Library_Tracker.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="300">
   <si>
     <t xml:space="preserve">AureonCare video library — production tracker</t>
   </si>
@@ -484,6 +484,9 @@
     <t xml:space="preserve">Do this before the visit, not after the denial.</t>
   </si>
   <si>
+    <t xml:space="preserve">Re-rendered against the merged UI.</t>
+  </si>
+  <si>
     <t xml:space="preserve">V10</t>
   </si>
   <si>
@@ -538,7 +541,7 @@
     <t xml:space="preserve">Prescribe and send electronically</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient chart ▸ Prescriptions</t>
+    <t xml:space="preserve">Clinical ▸ Diagnoses ▸ e-Prescribe</t>
   </si>
   <si>
     <t xml:space="preserve">New prescription → drug, dose, refills → interaction and allergy check fires → choose the patient's pharmacy → send via Surescripts → status → appears in portal.</t>
@@ -577,7 +580,7 @@
     <t xml:space="preserve">Diagnosis quality drives claim acceptance.</t>
   </si>
   <si>
-    <t xml:space="preserve">Re-recorded against the relocated nav (Clinical, not Patients) and the new patient picker on the standalone form. Narrated with google/en-US-Neural2-D to match the rest of the library.</t>
+    <t xml:space="preserve">Re-recorded against the relocated nav (Clinical, not Patients) and the new patient picker on the standalone form. Narrated with google/en-US-Neural2-D to match the rest of the library. Re-rendered against the merged UI.</t>
   </si>
   <si>
     <t xml:space="preserve">V16</t>
@@ -1728,7 +1731,7 @@
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">SUM('Video Tracker'!$G$3:$G$41)</f>
-        <v>69.2</v>
+        <v>73.4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1827,7 +1830,7 @@
       </c>
       <c r="F18" s="14" t="n">
         <f aca="false">SUMIF('Video Tracker'!$B$3:$B$41,$B18,'Video Tracker'!$G$3:$G$41)</f>
-        <v>16.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2993,7 +2996,7 @@
         <v>138</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>150</v>
@@ -3031,11 +3034,13 @@
         <v/>
       </c>
       <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
+      <c r="V12" s="25" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>38</v>
@@ -3044,22 +3049,22 @@
         <v>68</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>138</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J13" s="20" t="s">
         <v>67</v>
@@ -3091,11 +3096,13 @@
         <v/>
       </c>
       <c r="U13" s="25"/>
-      <c r="V13" s="25"/>
+      <c r="V13" s="25" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>38</v>
@@ -3104,22 +3111,22 @@
         <v>68</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>138</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J14" s="20" t="s">
         <v>67</v>
@@ -3151,11 +3158,13 @@
         <v/>
       </c>
       <c r="U14" s="25"/>
-      <c r="V14" s="25"/>
+      <c r="V14" s="25" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>38</v>
@@ -3164,22 +3173,22 @@
         <v>68</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J15" s="20" t="s">
         <v>67</v>
@@ -3211,11 +3220,13 @@
         <v/>
       </c>
       <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
+      <c r="V15" s="25" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>38</v>
@@ -3224,22 +3235,22 @@
         <v>68</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>127</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J16" s="20" t="s">
         <v>67</v>
@@ -3271,11 +3282,13 @@
         <v/>
       </c>
       <c r="U16" s="25"/>
-      <c r="V16" s="25"/>
+      <c r="V16" s="25" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>38</v>
@@ -3284,22 +3297,22 @@
         <v>68</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>127</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J17" s="20" t="s">
         <v>67</v>
@@ -3331,11 +3344,13 @@
         <v/>
       </c>
       <c r="U17" s="25"/>
-      <c r="V17" s="25"/>
+      <c r="V17" s="25" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B18" s="17" t="s">
         <v>38</v>
@@ -3344,22 +3359,22 @@
         <v>68</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>127</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J18" s="20" t="s">
         <v>69</v>
@@ -3394,12 +3409,12 @@
       </c>
       <c r="U18" s="25"/>
       <c r="V18" s="25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>38</v>
@@ -3408,22 +3423,22 @@
         <v>68</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I19" s="18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J19" s="20" t="s">
         <v>67</v>
@@ -3455,11 +3470,13 @@
         <v/>
       </c>
       <c r="U19" s="25"/>
-      <c r="V19" s="25"/>
+      <c r="V19" s="25" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>39</v>
@@ -3468,22 +3485,22 @@
         <v>71</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G20" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J20" s="20" t="s">
         <v>67</v>
@@ -3519,7 +3536,7 @@
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>39</v>
@@ -3528,10 +3545,10 @@
         <v>71</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>112</v>
@@ -3540,10 +3557,10 @@
         <v>1.5</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J21" s="20" t="s">
         <v>67</v>
@@ -3579,7 +3596,7 @@
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>39</v>
@@ -3588,10 +3605,10 @@
         <v>71</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>112</v>
@@ -3600,10 +3617,10 @@
         <v>2</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J22" s="20" t="s">
         <v>67</v>
@@ -3639,7 +3656,7 @@
     </row>
     <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>39</v>
@@ -3648,22 +3665,22 @@
         <v>71</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G23" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J23" s="20" t="s">
         <v>67</v>
@@ -3699,7 +3716,7 @@
     </row>
     <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>39</v>
@@ -3708,22 +3725,22 @@
         <v>71</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G24" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J24" s="20" t="s">
         <v>67</v>
@@ -3759,7 +3776,7 @@
     </row>
     <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>39</v>
@@ -3768,22 +3785,22 @@
         <v>71</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G25" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J25" s="20" t="s">
         <v>67</v>
@@ -3819,7 +3836,7 @@
     </row>
     <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>39</v>
@@ -3828,22 +3845,22 @@
         <v>71</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G26" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J26" s="20" t="s">
         <v>67</v>
@@ -3879,7 +3896,7 @@
     </row>
     <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B27" s="17" t="s">
         <v>40</v>
@@ -3888,22 +3905,22 @@
         <v>73</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G27" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J27" s="20" t="s">
         <v>67</v>
@@ -3939,7 +3956,7 @@
     </row>
     <row r="28" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B28" s="17" t="s">
         <v>40</v>
@@ -3948,22 +3965,22 @@
         <v>73</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G28" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J28" s="20" t="s">
         <v>67</v>
@@ -3999,7 +4016,7 @@
     </row>
     <row r="29" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B29" s="17" t="s">
         <v>40</v>
@@ -4008,22 +4025,22 @@
         <v>73</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G29" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J29" s="20" t="s">
         <v>67</v>
@@ -4059,7 +4076,7 @@
     </row>
     <row r="30" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B30" s="17" t="s">
         <v>40</v>
@@ -4068,22 +4085,22 @@
         <v>73</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G30" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J30" s="20" t="s">
         <v>67</v>
@@ -4119,7 +4136,7 @@
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>40</v>
@@ -4128,22 +4145,22 @@
         <v>73</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G31" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J31" s="20" t="s">
         <v>67</v>
@@ -4179,7 +4196,7 @@
     </row>
     <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B32" s="17" t="s">
         <v>40</v>
@@ -4188,22 +4205,22 @@
         <v>73</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G32" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J32" s="20" t="s">
         <v>67</v>
@@ -4239,7 +4256,7 @@
     </row>
     <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B33" s="17" t="s">
         <v>40</v>
@@ -4248,22 +4265,22 @@
         <v>73</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G33" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J33" s="20" t="s">
         <v>67</v>
@@ -4299,7 +4316,7 @@
     </row>
     <row r="34" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B34" s="17" t="s">
         <v>40</v>
@@ -4308,22 +4325,22 @@
         <v>73</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G34" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J34" s="20" t="s">
         <v>67</v>
@@ -4359,7 +4376,7 @@
     </row>
     <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B35" s="17" t="s">
         <v>40</v>
@@ -4368,22 +4385,22 @@
         <v>73</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G35" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I35" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J35" s="20" t="s">
         <v>67</v>
@@ -4419,7 +4436,7 @@
     </row>
     <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>41</v>
@@ -4428,10 +4445,10 @@
         <v>75</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>105</v>
@@ -4440,7 +4457,7 @@
         <v>1.5</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I36" s="18"/>
       <c r="J36" s="20" t="s">
@@ -4477,7 +4494,7 @@
     </row>
     <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>41</v>
@@ -4486,7 +4503,7 @@
         <v>75</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>111</v>
@@ -4498,7 +4515,7 @@
         <v>1.5</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I37" s="18"/>
       <c r="J37" s="20" t="s">
@@ -4535,7 +4552,7 @@
     </row>
     <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>41</v>
@@ -4544,10 +4561,10 @@
         <v>75</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>127</v>
@@ -4556,7 +4573,7 @@
         <v>1.5</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I38" s="18"/>
       <c r="J38" s="20" t="s">
@@ -4593,7 +4610,7 @@
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B39" s="17" t="s">
         <v>41</v>
@@ -4602,19 +4619,19 @@
         <v>75</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G39" s="19" t="n">
         <v>2</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I39" s="18"/>
       <c r="J39" s="20" t="s">
@@ -4651,7 +4668,7 @@
     </row>
     <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>41</v>
@@ -4660,10 +4677,10 @@
         <v>75</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>105</v>
@@ -4672,7 +4689,7 @@
         <v>1.5</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I40" s="18"/>
       <c r="J40" s="20" t="s">
@@ -4709,7 +4726,7 @@
     </row>
     <row r="41" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B41" s="17" t="s">
         <v>41</v>
@@ -4718,7 +4735,7 @@
         <v>75</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E41" s="18" t="s">
         <v>117</v>
@@ -4730,7 +4747,7 @@
         <v>1.5</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I41" s="18"/>
       <c r="J41" s="20" t="s">
@@ -4792,7 +4809,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{389B8875-14B1-4113-ABEC-61DA4FC43B80}</x14:id>
+          <x14:id>{B0E36FCA-5E8C-4F83-855A-1AA2F342F629}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4831,7 +4848,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{389B8875-14B1-4113-ABEC-61DA4FC43B80}">
+          <x14:cfRule type="dataBar" id="{B0E36FCA-5E8C-4F83-855A-1AA2F342F629}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
